--- a/output/pdf_financials_xlsx/RET.A.xlsx
+++ b/output/pdf_financials_xlsx/RET.A.xlsx
@@ -2174,19 +2174,19 @@
         <v>77.91500000000001</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>25.502</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>103.004</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>116.653</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>158.116</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>150.956</v>
       </c>
     </row>
     <row r="35">
@@ -2278,19 +2278,19 @@
         <v>77.91500000000001</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>25.502</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>103.004</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>116.653</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>158.116</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>150.956</v>
       </c>
     </row>
     <row r="37">
@@ -2902,19 +2902,19 @@
         <v>32.1</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>68.092</v>
+        <v>42.59</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>120.314</v>
+        <v>17.31</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>134.376</v>
+        <v>17.723</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>183.116</v>
+        <v>25</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>163.186</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="49">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -13919,7 +13919,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -16449,7 +16449,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">

--- a/output/pdf_financials_xlsx/RET.A.xlsx
+++ b/output/pdf_financials_xlsx/RET.A.xlsx
@@ -1913,13 +1913,13 @@
         <v>0</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>34.314</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>39.364</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>41.43</v>
       </c>
     </row>
     <row r="29">
@@ -1965,13 +1965,13 @@
         <v>42.856</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>14.319</v>
+        <v>48.633</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>7.877</v>
+        <v>47.241</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-5.144</v>
+        <v>36.286</v>
       </c>
     </row>
     <row r="30">
@@ -2017,13 +2017,13 @@
         <v>5.335172475609164</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>1.801839212370138</v>
+        <v>6.119760207779657</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>1.017958035885056</v>
+        <v>6.105034349783666</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-0.6621647018842859</v>
+        <v>4.670938641635536</v>
       </c>
     </row>
     <row r="31">
@@ -5599,13 +5599,13 @@
         <v>0</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>34.314</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>39.364</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>41.43</v>
       </c>
     </row>
     <row r="101">
@@ -38493,7 +38493,11 @@
           <t>Depreciation on right-of-use assets 7</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RET.A.xlsx
+++ b/output/pdf_financials_xlsx/RET.A.xlsx
@@ -1247,10 +1247,10 @@
         <v>-2.654</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-4.112</v>
+        <v>4.112</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.426</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-23.829</v>
@@ -1259,7 +1259,7 @@
         <v>-0.191</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>15.452</v>
+        <v>-0.42</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-32.098</v>
@@ -1271,7 +1271,7 @@
         <v>3.762</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.176</v>
       </c>
     </row>
     <row r="18">
@@ -1465,16 +1465,14 @@
       <c r="H20" s="3" t="n">
         <v>13.415</v>
       </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="3" t="n">
+        <v>-27.555</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-87.426</v>
+        <v>-73.16200000000001</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-172.217</v>
+        <v>-100.036</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>143.224</v>
@@ -1488,10 +1486,8 @@
       <c r="O20" s="3" t="n">
         <v>12.139</v>
       </c>
-      <c r="P20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P20" s="3" t="n">
+        <v>-1.268</v>
       </c>
     </row>
     <row r="21">
@@ -1626,7 +1622,7 @@
         <v>13.415</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>-26.129</v>
+        <v>-27.555</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-87.426</v>
@@ -1647,7 +1643,7 @@
         <v>12.139</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>-1.092</v>
+        <v>-1.268</v>
       </c>
     </row>
     <row r="24">
@@ -2054,7 +2050,7 @@
         <v>23.46094596907628</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-0</v>
+        <v>-5.457537601898274</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-48.30235339427969</v>
@@ -2063,7 +2059,7 @@
         <v>-0.1912965095898643</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>10.82042519817372</v>
+        <v>0.2941094087000364</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>70.43823652044154</v>
@@ -2075,7 +2071,7 @@
         <v>23.65888937802654</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0</v>
+        <v>-16.11721611721612</v>
       </c>
     </row>
     <row r="32">
@@ -2106,7 +2102,7 @@
         <v>1.42807565873516</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>-2.788119361258277</v>
+        <v>-2.940282023784753</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>-12.3927650043943</v>
@@ -2127,7 +2123,7 @@
         <v>1.56874350610749</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>-0.1405684009443313</v>
+        <v>-0.1632241139170441</v>
       </c>
     </row>
     <row r="33">
@@ -5532,7 +5528,7 @@
         <v>13.415</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>-26.129</v>
+        <v>-27.555</v>
       </c>
       <c r="J99" s="3" t="n">
         <v>-87.426</v>
@@ -5553,7 +5549,7 @@
         <v>12.139</v>
       </c>
       <c r="P99" s="3" t="n">
-        <v>-1.092</v>
+        <v>-1.268</v>
       </c>
     </row>
     <row r="100">
@@ -6291,28 +6287,28 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-17.403</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-12.951</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-20.803</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-39.904</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0</v>
+        <v>-5.66</v>
       </c>
       <c r="J114" s="3" t="n">
         <v>0</v>
@@ -6343,13 +6339,13 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>4.642</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>4.694</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>1.709</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -6358,16 +6354,16 @@
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>33.408</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>1.678</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>41.425</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -48080,7 +48076,11 @@
           <t>Proceeds on sale of marketable securities 19</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
           <t>-</t>
@@ -50022,7 +50022,11 @@
           <t>Purchases of marketable securities</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E479" t="inlineStr">
         <is>
           <t>-</t>
@@ -50109,7 +50113,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E480" t="inlineStr">
         <is>
           <t>-</t>
@@ -53675,7 +53683,11 @@
           <t>Purchases of marketable securities</t>
         </is>
       </c>
-      <c r="D520" t="inlineStr"/>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E520" t="inlineStr">
         <is>
           <t>-</t>
@@ -53764,7 +53776,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D521" t="inlineStr"/>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E521" t="inlineStr">
         <is>
           <t>-</t>
@@ -54573,7 +54589,11 @@
           <t>Purchases of marketable securities</t>
         </is>
       </c>
-      <c r="D530" t="inlineStr"/>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E530" s="5" t="n">
         <v>-17.403</v>
       </c>
@@ -55981,7 +56001,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D546" t="inlineStr"/>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E546" t="inlineStr">
         <is>
           <t>-</t>
@@ -56070,7 +56094,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D547" t="inlineStr"/>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E547" s="5" t="n">
         <v>4.642</v>
       </c>
@@ -56511,7 +56539,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E552" s="5" t="n">
         <v>-5.148</v>
       </c>
@@ -60631,7 +60663,11 @@
           <t>Income tax recovery (expense) 9</t>
         </is>
       </c>
-      <c r="D598" t="inlineStr"/>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E598" t="inlineStr">
         <is>
           <t>-</t>
@@ -64283,7 +64319,11 @@
           <t>Income tax recovery 12</t>
         </is>
       </c>
-      <c r="D638" t="inlineStr"/>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E638" t="inlineStr">
         <is>
           <t>-</t>
@@ -66200,7 +66240,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D659" t="inlineStr"/>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E659" t="inlineStr">
         <is>
           <t>-</t>
